--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2019_los_lagos.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2019_los_lagos.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:38</t>
+    <t xml:space="preserve">2026-10-05 01:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -723,10 +723,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>697685.62</v>
+        <v>697685.63</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>692601.94</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -822,7 +822,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>773460.12</v>
+        <v>773460.13</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>876986.31</v>
@@ -836,7 +836,7 @@
         <v>707033.31</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -877,7 +877,7 @@
         <v>19</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>733415.62</v>
+        <v>733415.63</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>844285.88</v>
@@ -910,10 +910,10 @@
         <v>22</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>736770.12</v>
+        <v>736770.13</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -943,7 +943,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>761273.62</v>
+        <v>761273.63</v>
       </c>
       <c r="C24" s="2" t="n">
         <v>864071.75</v>
@@ -954,7 +954,7 @@
         <v>26</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>821071.62</v>
+        <v>821071.63</v>
       </c>
       <c r="C25" s="2" t="n">
         <v>928044.19</v>
@@ -1001,7 +1001,7 @@
         <v>786085.31</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1012,7 +1012,7 @@
         <v>782772.44</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1097,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>802650.62</v>
+        <v>802650.63</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>917146.44</v>
@@ -1166,7 +1166,7 @@
         <v>841824</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1218,7 +1218,7 @@
         <v>50</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>936977.12</v>
+        <v>936977.13</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>1049309.75</v>
@@ -1284,10 +1284,10 @@
         <v>56</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>939606.12</v>
+        <v>939606.13</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1295,10 +1295,10 @@
         <v>57</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>937587.12</v>
+        <v>937587.13</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1328,7 +1328,7 @@
         <v>60</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>962401.62</v>
+        <v>962401.63</v>
       </c>
       <c r="C59" s="2" t="n">
         <v>1086115.25</v>
@@ -1342,7 +1342,7 @@
         <v>974519.56</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1350,7 +1350,7 @@
         <v>62</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1056450.62</v>
+        <v>1056450.63</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>1183065.88</v>
@@ -1364,7 +1364,7 @@
         <v>1016973.94</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1419,7 +1419,7 @@
         <v>1061277.38</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1427,7 +1427,7 @@
         <v>69</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>1048770.12</v>
+        <v>1048770.13</v>
       </c>
       <c r="C68" s="2" t="n">
         <v>1185328.75</v>
@@ -1438,7 +1438,7 @@
         <v>70</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1048667.62</v>
+        <v>1048667.63</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>1186515.5</v>
@@ -1449,7 +1449,7 @@
         <v>71</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>1111481.12</v>
+        <v>1111481.13</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>1246393.5</v>
@@ -1460,7 +1460,7 @@
         <v>72</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>1070570.62</v>
+        <v>1070570.63</v>
       </c>
       <c r="C71" s="2" t="n">
         <v>1202545</v>
@@ -1515,10 +1515,10 @@
         <v>77</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>1097899.62</v>
+        <v>1097899.63</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1537,7 +1537,7 @@
         <v>79</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>1108613.12</v>
+        <v>1108613.13</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>1242222.38</v>
@@ -1548,10 +1548,10 @@
         <v>80</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>1124041.12</v>
+        <v>1124041.13</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1559,10 +1559,10 @@
         <v>81</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>1125269.12</v>
+        <v>1125269.13</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1584,7 +1584,7 @@
         <v>1183735.38</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
